--- a/LIST_De_tai_Chung.xlsx
+++ b/LIST_De_tai_Chung.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\THUY CQ\PM DANG KY DE TAI LV\C My Dung\2026\CH33D3&amp;D1\De tai LV, de an CHK33 Khoa CM gửi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\THUY CQ\PM DANG KY DE TAI LV\HeThongDangKy\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="De tai" sheetId="1" r:id="rId1"/>
@@ -11098,6 +11098,54 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 1266"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7820025" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -35560,7 +35608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="3"/>
@@ -35569,29 +35617,43 @@
     <col min="5" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="1" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>9</v>
@@ -35599,13 +35661,13 @@
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>9</v>
@@ -35613,13 +35675,13 @@
     </row>
     <row r="5" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>9</v>
@@ -35627,27 +35689,27 @@
     </row>
     <row r="6" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
@@ -35655,27 +35717,27 @@
     </row>
     <row r="8" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>17</v>
@@ -35683,27 +35745,27 @@
     </row>
     <row r="10" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>20</v>
@@ -35711,13 +35773,13 @@
     </row>
     <row r="12" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="4">
-        <v>8</v>
-      </c>
       <c r="C12" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>20</v>
@@ -35725,13 +35787,13 @@
     </row>
     <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>20</v>
@@ -35739,13 +35801,13 @@
     </row>
     <row r="14" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>20</v>
@@ -35753,13 +35815,13 @@
     </row>
     <row r="15" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>20</v>
@@ -35767,27 +35829,27 @@
     </row>
     <row r="16" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>27</v>
@@ -35795,13 +35857,13 @@
     </row>
     <row r="18" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>27</v>
@@ -35809,13 +35871,13 @@
     </row>
     <row r="19" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>27</v>
@@ -35823,43 +35885,29 @@
     </row>
     <row r="20" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4">
         <v>19</v>
       </c>
-      <c r="B21" s="4">
-        <v>3</v>
-      </c>
       <c r="C21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4">
-        <v>19</v>
-      </c>
-      <c r="C22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>34</v>
       </c>
     </row>
